--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios166.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios166.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30181.83218044145</v>
+        <v>15988.48453945535</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21663.94871372132</v>
+        <v>14974.58436890033</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13021.35757607422</v>
+        <v>14177.69861177535</v>
       </c>
     </row>
     <row r="9">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19729.26265805569</v>
+        <v>17561.85889177746</v>
       </c>
     </row>
     <row r="12">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4932.315664513923</v>
+        <v>4390.464722944364</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36111.65144163276</v>
+        <v>47512.38641506997</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12073.74991594462</v>
+        <v>11151.15250362191</v>
       </c>
     </row>
     <row r="18">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>23922.55352577161</v>
+        <v>36404.50676322409</v>
       </c>
     </row>
     <row r="21">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>23761.89576247715</v>
+        <v>34463.2087029625</v>
       </c>
     </row>
     <row r="24">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12619.09796218044</v>
+        <v>7859.923662353119</v>
       </c>
     </row>
     <row r="27">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>20454.04124368032</v>
+        <v>16803.24072151732</v>
       </c>
     </row>
     <row r="30">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5113.51031092008</v>
+        <v>4200.81018037933</v>
       </c>
     </row>
     <row r="32">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>43515.57231339005</v>
+        <v>62750.0640195439</v>
       </c>
     </row>
     <row r="33">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>17272.68025239224</v>
+        <v>14757.26088913716</v>
       </c>
     </row>
     <row r="36">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>16228.89528097737</v>
+        <v>24689.06528252661</v>
       </c>
     </row>
     <row r="39">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>19592.72418647578</v>
+        <v>16467.99846276824</v>
       </c>
     </row>
     <row r="42">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>22924.86359083833</v>
+        <v>9940.474826924203</v>
       </c>
     </row>
     <row r="45">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>13772.05187006462</v>
+        <v>16899.39459472226</v>
       </c>
     </row>
     <row r="48">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3443.012967516155</v>
+        <v>4224.848648680566</v>
       </c>
     </row>
     <row r="50">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>29693.67987935362</v>
+        <v>54154.91496678651</v>
       </c>
     </row>
     <row r="51">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>15254.28779375457</v>
+        <v>18888.97683011464</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>9421.601096695944</v>
+        <v>19848.39823908904</v>
       </c>
     </row>
     <row r="57">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>23235.44567520671</v>
+        <v>17304.7356433357</v>
       </c>
     </row>
     <row r="60">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>20546.84346903683</v>
+        <v>12092.80071189521</v>
       </c>
     </row>
     <row r="63">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10730.3844670796</v>
+        <v>26190.43388308435</v>
       </c>
     </row>
     <row r="66">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2682.5961167699</v>
+        <v>6547.608470771088</v>
       </c>
     </row>
     <row r="68">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>20270.5327139193</v>
+        <v>28296.75549858945</v>
       </c>
     </row>
     <row r="69">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6878.070492658632</v>
+        <v>17951.12806578105</v>
       </c>
     </row>
     <row r="72">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>31737.69676260239</v>
+        <v>23709.76478413248</v>
       </c>
     </row>
     <row r="75">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>33435.82539989359</v>
+        <v>19492.5999826497</v>
       </c>
     </row>
     <row r="78">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>10577.79201133059</v>
+        <v>6499.290174641903</v>
       </c>
     </row>
     <row r="81">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24099.27442400641</v>
+        <v>24239.12464052377</v>
       </c>
     </row>
     <row r="84">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6024.818606001603</v>
+        <v>6059.781160130941</v>
       </c>
     </row>
     <row r="86">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>70853.82991267984</v>
+        <v>47432.43207137698</v>
       </c>
     </row>
     <row r="87">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>19202.54905411185</v>
+        <v>13140.1455603294</v>
       </c>
     </row>
     <row r="90">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>23152.48539115114</v>
+        <v>18243.91194241477</v>
       </c>
     </row>
     <row r="93">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7738.962117475098</v>
+        <v>22606.77974311732</v>
       </c>
     </row>
     <row r="96">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>9421.704040963674</v>
+        <v>10675.32032616973</v>
       </c>
     </row>
     <row r="99">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>17439.17483038846</v>
+        <v>19396.44136773076</v>
       </c>
     </row>
     <row r="102">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4359.793707597114</v>
+        <v>4849.110341932689</v>
       </c>
     </row>
     <row r="104">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>46115.91805132414</v>
+        <v>39956.71510436285</v>
       </c>
     </row>
     <row r="105">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>11795.5272462173</v>
+        <v>6746.821397422919</v>
       </c>
     </row>
     <row r="108">
